--- a/SGC-CKN/Excel/5f8a75e9-2c9a-4ea4-8cc6-bdf0cfa34b37_Lô_CT-02_P1-3_D800_03-04-2026.xlsx
+++ b/SGC-CKN/Excel/5f8a75e9-2c9a-4ea4-8cc6-bdf0cfa34b37_Lô_CT-02_P1-3_D800_03-04-2026.xlsx
@@ -1263,16 +1263,16 @@
         <v>-8</v>
       </c>
       <c r="G14" s="16">
-        <v>-14.7</v>
+        <v>-12.7</v>
       </c>
       <c r="H14" s="16">
         <v>0.3</v>
       </c>
       <c r="I14" s="16">
-        <v>6.7</v>
+        <v>4.7</v>
       </c>
       <c r="J14" s="15">
-        <v>22.33</v>
+        <v>15.67</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1295,7 +1295,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="19">
-        <v>-14.7</v>
+        <v>-12.7</v>
       </c>
       <c r="G15" s="19">
         <v>-20.8</v>
@@ -1304,10 +1304,10 @@
         <v>1.47</v>
       </c>
       <c r="I15" s="19">
-        <v>6.1</v>
-      </c>
-      <c r="J15" s="8">
-        <v>4.16</v>
+        <v>8.1</v>
+      </c>
+      <c r="J15" s="15">
+        <v>5.52</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1657,16 +1657,16 @@
         <v>-8</v>
       </c>
       <c r="F5" s="16">
-        <v>-14.7</v>
+        <v>-12.7</v>
       </c>
       <c r="G5" s="16">
         <v>0.3</v>
       </c>
       <c r="H5" s="16">
-        <v>6.7</v>
+        <v>4.7</v>
       </c>
       <c r="I5" s="15">
-        <v>22.33</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-14.7</v>
+        <v>-12.7</v>
       </c>
       <c r="F6" s="19">
         <v>-20.8</v>
@@ -1692,10 +1692,10 @@
         <v>1.47</v>
       </c>
       <c r="H6" s="19">
-        <v>6.1</v>
-      </c>
-      <c r="I6" s="8">
-        <v>4.16</v>
+        <v>8.1</v>
+      </c>
+      <c r="I6" s="15">
+        <v>5.52</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
